--- a/teaching_statement.xlsx
+++ b/teaching_statement.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sri\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sri\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7EFB38-6BB8-4E5B-B15D-F0B00E2124B8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{359A383B-D77B-4175-9C89-C3528EF03F4F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="74">
   <si>
     <t>2016-17</t>
   </si>
@@ -236,6 +236,12 @@
   </si>
   <si>
     <t>IIM Calcutta</t>
+  </si>
+  <si>
+    <t>2025-26</t>
+  </si>
+  <si>
+    <t>IIFT Kolkata</t>
   </si>
 </sst>
 </file>
@@ -695,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18.85546875" customWidth="1"/>
@@ -1507,6 +1513,26 @@
         <v>71</v>
       </c>
     </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="5">
+        <v>20</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
